--- a/published/03_Tenders_Master.xlsx
+++ b/published/03_Tenders_Master.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>REVISED- SUPPLY DELIVER INSTALL SERVICE AND REFILL OF LP GAS 
+          <t>REVISED- SUPPLY DELIVER INSTALL SERVICE AND REFILL OF LP GAS
 TO THE PPECB LABORATORY IN CENTURION</t>
         </is>
       </c>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Storage rental space for the South African Environmental Observation Network: Egagasini 
+          <t>Storage rental space for the South African Environmental Observation Network: Egagasini
  Nodes Marine Sampling Equipment based in Cape Town for a period of five (5) years</t>
         </is>
       </c>
